--- a/artfynd/A 26659-2025 artfynd.xlsx
+++ b/artfynd/A 26659-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017121</v>
       </c>
       <c r="B2" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26659-2025 artfynd.xlsx
+++ b/artfynd/A 26659-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017121</v>
       </c>
       <c r="B2" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26659-2025 artfynd.xlsx
+++ b/artfynd/A 26659-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017121</v>
       </c>
       <c r="B2" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26659-2025 artfynd.xlsx
+++ b/artfynd/A 26659-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017121</v>
       </c>
       <c r="B2" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26659-2025 artfynd.xlsx
+++ b/artfynd/A 26659-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017121</v>
       </c>
       <c r="B2" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26659-2025 artfynd.xlsx
+++ b/artfynd/A 26659-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017121</v>
       </c>
       <c r="B2" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26659-2025 artfynd.xlsx
+++ b/artfynd/A 26659-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017121</v>
       </c>
       <c r="B2" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26659-2025 artfynd.xlsx
+++ b/artfynd/A 26659-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017121</v>
       </c>
       <c r="B2" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26659-2025 artfynd.xlsx
+++ b/artfynd/A 26659-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017121</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
